--- a/batchstudent/Result/anlpvhe187047/TC1/GradeDetail.xlsx
+++ b/batchstudent/Result/anlpvhe187047/TC1/GradeDetail.xlsx
@@ -158,34 +158,16 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
-    <x:t>SYN_SENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASS</x:t>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIL</x:t>
   </x:si>
   <x:si>
     <x:t>SYN, ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Server responding (SYN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST-ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RESET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -212,7 +194,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -221,17 +203,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -254,7 +226,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="5">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -264,14 +236,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -281,14 +247,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -915,11 +873,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:R4"/>
+  <x:dimension ref="A1:R3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1026,25 +984,25 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P2" s="0">
-        <x:v>54906</x:v>
-      </x:c>
-      <x:c r="Q2" s="0">
-        <x:v>4000</x:v>
+      <x:c r="P2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q2" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>47</x:v>
@@ -1082,7 +1040,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
         <x:v>17</x:v>
@@ -1102,64 +1060,8 @@
       <x:c r="Q3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R3" s="3" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:18">
-      <x:c r="A4" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="M4" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P4" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q4" s="0">
-        <x:v>54906</x:v>
-      </x:c>
-      <x:c r="R4" s="4" t="s">
-        <x:v>55</x:v>
+      <x:c r="R3" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
